--- a/hardware/electronics/work_on_progree_pn5180_board/production/positions.xlsx
+++ b/hardware/electronics/work_on_progree_pn5180_board/production/positions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ludwin/Elektronik/abr/hardware/electronics/pn5180_board/production/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ludwin/Elektronik/abr/hardware/electronics/work_on_progree_pn5180_board/production/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1360075F-9334-4747-9B90-461799DEB6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A692652-7A01-0B43-9479-7993B2E7C407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6580" yWindow="1700" windowWidth="27440" windowHeight="15980" xr2:uid="{ABC6D1CC-45C4-C348-B501-329F6635E911}"/>
+    <workbookView xWindow="8360" yWindow="1060" windowWidth="27440" windowHeight="15980" xr2:uid="{115A2A4E-5818-C14C-AE04-18331C57C914}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -43,8 +43,8 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{BA16F7B1-C9F9-9343-960D-C0188698AA97}" name="positions" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr codePage="65001" sourceFile="/Users/ludwin/Elektronik/abr/hardware/electronics/pn5180_board/production/positions.csv" decimal="," thousands="." comma="1">
+  <connection id="1" xr16:uid="{547C20BB-BCB3-2A42-95C3-DBA6F82A0760}" name="positions" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="65001" sourceFile="/Users/ludwin/Elektronik/abr/hardware/electronics/work_on_progree_pn5180_board/production/positions.csv" decimal="," thousands="." comma="1" semicolon="1">
       <textFields count="5">
         <textField type="text"/>
         <textField type="text"/>
@@ -93,9 +93,24 @@
     <t>C10</t>
   </si>
   <si>
+    <t>108.85</t>
+  </si>
+  <si>
+    <t>-131.265</t>
+  </si>
+  <si>
+    <t>270.0</t>
+  </si>
+  <si>
     <t>C11</t>
   </si>
   <si>
+    <t>107.35</t>
+  </si>
+  <si>
+    <t>-131.835</t>
+  </si>
+  <si>
     <t>C12</t>
   </si>
   <si>
@@ -150,9 +165,6 @@
     <t>-112.5</t>
   </si>
   <si>
-    <t>270.0</t>
-  </si>
-  <si>
     <t>C18</t>
   </si>
   <si>
@@ -195,12 +207,6 @@
     <t>136.0</t>
   </si>
   <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>-111.5</t>
-  </si>
-  <si>
     <t>C29</t>
   </si>
   <si>
@@ -222,15 +228,6 @@
     <t>-116.8</t>
   </si>
   <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>135.995</t>
-  </si>
-  <si>
-    <t>-118.5</t>
-  </si>
-  <si>
     <t>C33</t>
   </si>
   <si>
@@ -276,16 +273,22 @@
     <t>C6</t>
   </si>
   <si>
+    <t>105.87</t>
+  </si>
+  <si>
     <t>C7</t>
   </si>
   <si>
+    <t>104.42</t>
+  </si>
+  <si>
     <t>C8</t>
   </si>
   <si>
-    <t>124.19</t>
-  </si>
-  <si>
-    <t>-122.065</t>
+    <t>125.945</t>
+  </si>
+  <si>
+    <t>-121.15</t>
   </si>
   <si>
     <t>C9</t>
@@ -375,6 +378,21 @@
     <t>-127.38</t>
   </si>
   <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>140.32</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>140.36</t>
+  </si>
+  <si>
+    <t>-108.98</t>
+  </si>
+  <si>
     <t>R2</t>
   </si>
   <si>
@@ -460,43 +478,19 @@
   </si>
   <si>
     <t>-115.01</t>
-  </si>
-  <si>
-    <t>108.85</t>
-  </si>
-  <si>
-    <t>107.35</t>
-  </si>
-  <si>
-    <t>-131.265</t>
-  </si>
-  <si>
-    <t>-131.835</t>
-  </si>
-  <si>
-    <t>105.87</t>
-  </si>
-  <si>
-    <t>104.42</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -519,10 +513,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -541,7 +534,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="positions" connectionId="1" xr16:uid="{91247730-2BB3-0349-B734-30C9AC571399}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="positions" connectionId="1" xr16:uid="{CA3047E4-A81E-9443-BEA6-8A6C77146118}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -860,15 +853,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE960EEC-F084-2D40-9C8A-956CB1149014}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439BB88B-23FA-E347-8B84-69F59D253CA3}">
   <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -910,44 +903,44 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
@@ -958,13 +951,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>8</v>
@@ -975,16 +968,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>9</v>
@@ -992,16 +985,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>9</v>
@@ -1009,16 +1002,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>9</v>
@@ -1026,16 +1019,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>9</v>
@@ -1043,16 +1036,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>9</v>
@@ -1060,13 +1053,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>8</v>
@@ -1077,16 +1070,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>9</v>
@@ -1094,13 +1087,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>8</v>
@@ -1111,16 +1104,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>9</v>
@@ -1128,16 +1121,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>9</v>
@@ -1145,16 +1138,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>9</v>
@@ -1162,16 +1155,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>9</v>
@@ -1179,16 +1172,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>9</v>
@@ -1196,16 +1189,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>9</v>
@@ -1213,16 +1206,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>9</v>
@@ -1230,13 +1223,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>8</v>
@@ -1247,13 +1240,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>8</v>
@@ -1264,13 +1257,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>8</v>
@@ -1281,13 +1274,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>8</v>
@@ -1298,16 +1291,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>9</v>
@@ -1315,16 +1308,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>9</v>
@@ -1332,16 +1325,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>9</v>
@@ -1349,50 +1342,50 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>9</v>
@@ -1400,16 +1393,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>9</v>
@@ -1417,16 +1410,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>9</v>
@@ -1434,16 +1427,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>9</v>
@@ -1451,16 +1444,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>9</v>
@@ -1468,16 +1461,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>9</v>
@@ -1485,16 +1478,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>9</v>
@@ -1502,16 +1495,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>9</v>
@@ -1519,16 +1512,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>9</v>
@@ -1536,16 +1529,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>9</v>
@@ -1553,16 +1546,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>9</v>
@@ -1570,16 +1563,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>9</v>
@@ -1587,16 +1580,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>9</v>
@@ -1604,16 +1597,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>9</v>
@@ -1621,16 +1614,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>9</v>
@@ -1638,16 +1631,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>9</v>
@@ -1655,16 +1648,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>9</v>
@@ -1672,13 +1665,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>8</v>
@@ -1689,16 +1682,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>9</v>
@@ -1706,16 +1699,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>9</v>
@@ -1723,13 +1716,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>8</v>
